--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815902</v>
+        <v>119815905</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,50 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489634</v>
+        <v>489652</v>
       </c>
       <c r="R4" t="n">
-        <v>6949843</v>
+        <v>6949845</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,12 +999,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815905</v>
+        <v>119815902</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,41 +1135,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489652</v>
+        <v>489634</v>
       </c>
       <c r="R6" t="n">
-        <v>6949845</v>
+        <v>6949843</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815905</v>
+        <v>119815546</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489652</v>
+        <v>489670</v>
       </c>
       <c r="R4" t="n">
-        <v>6949845</v>
+        <v>6949842</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815546</v>
+        <v>119815902</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489670</v>
+        <v>489634</v>
       </c>
       <c r="R5" t="n">
-        <v>6949842</v>
+        <v>6949843</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815902</v>
+        <v>119815859</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,47 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489634</v>
+        <v>489648</v>
       </c>
       <c r="R6" t="n">
-        <v>6949843</v>
+        <v>6949845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815859</v>
+        <v>119815905</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489648</v>
+        <v>489652</v>
       </c>
       <c r="R8" t="n">
         <v>6949845</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,12 +1465,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815546</v>
+        <v>119815905</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489670</v>
+        <v>489652</v>
       </c>
       <c r="R4" t="n">
-        <v>6949842</v>
+        <v>6949845</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815902</v>
+        <v>119815546</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489634</v>
+        <v>489670</v>
       </c>
       <c r="R5" t="n">
-        <v>6949843</v>
+        <v>6949842</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,12 +1111,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1244,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119816036</v>
+        <v>119815902</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1279,7 +1270,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1293,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489554</v>
+        <v>489634</v>
       </c>
       <c r="R7" t="n">
-        <v>6949859</v>
+        <v>6949843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815905</v>
+        <v>119816036</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,41 +1368,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489652</v>
+        <v>489554</v>
       </c>
       <c r="R8" t="n">
-        <v>6949845</v>
+        <v>6949859</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,12 +1465,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815905</v>
+        <v>119815902</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489652</v>
+        <v>489634</v>
       </c>
       <c r="R4" t="n">
-        <v>6949845</v>
+        <v>6949843</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815546</v>
+        <v>119815905</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489670</v>
+        <v>489652</v>
       </c>
       <c r="R5" t="n">
-        <v>6949842</v>
+        <v>6949845</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815859</v>
+        <v>119816036</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1144,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489648</v>
+        <v>489554</v>
       </c>
       <c r="R6" t="n">
-        <v>6949845</v>
+        <v>6949859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815902</v>
+        <v>119815859</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,47 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489634</v>
+        <v>489648</v>
       </c>
       <c r="R7" t="n">
-        <v>6949843</v>
+        <v>6949845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1353,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119816036</v>
+        <v>119815546</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,50 +1377,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489554</v>
+        <v>489670</v>
       </c>
       <c r="R8" t="n">
-        <v>6949859</v>
+        <v>6949842</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,12 +1465,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815902</v>
+        <v>119816036</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489634</v>
+        <v>489554</v>
       </c>
       <c r="R4" t="n">
-        <v>6949843</v>
+        <v>6949859</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815905</v>
+        <v>119815902</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,41 +1032,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489652</v>
+        <v>489634</v>
       </c>
       <c r="R5" t="n">
-        <v>6949845</v>
+        <v>6949843</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119816036</v>
+        <v>119815905</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,50 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489554</v>
+        <v>489652</v>
       </c>
       <c r="R6" t="n">
-        <v>6949859</v>
+        <v>6949845</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,12 +1241,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -1253,7 +1253,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815859</v>
+        <v>119815546</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489648</v>
+        <v>489670</v>
       </c>
       <c r="R7" t="n">
-        <v>6949845</v>
+        <v>6949842</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,19 +1353,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815546</v>
+        <v>119815859</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489670</v>
+        <v>489648</v>
       </c>
       <c r="R8" t="n">
-        <v>6949842</v>
+        <v>6949845</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,12 +1465,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117566267</v>
       </c>
       <c r="B2" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -787,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117566902</v>
+        <v>119815905</v>
       </c>
       <c r="B3" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489669</v>
+        <v>489652</v>
       </c>
       <c r="R3" t="n">
-        <v>6949829</v>
+        <v>6949845</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816036</v>
+        <v>117566902</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489554</v>
+        <v>489669</v>
       </c>
       <c r="R4" t="n">
-        <v>6949859</v>
+        <v>6949829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815902</v>
+        <v>119815546</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,46 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489634</v>
+        <v>489670</v>
       </c>
       <c r="R5" t="n">
-        <v>6949843</v>
+        <v>6949842</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,49 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815905</v>
+        <v>119815720</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489652</v>
+        <v>489670</v>
       </c>
       <c r="R6" t="n">
-        <v>6949845</v>
+        <v>6949846</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,31 +1198,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815546</v>
+        <v>119815859</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1293,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489670</v>
+        <v>489648</v>
       </c>
       <c r="R7" t="n">
-        <v>6949842</v>
+        <v>6949845</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,62 +1305,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815859</v>
+        <v>119815902</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489648</v>
+        <v>489634</v>
       </c>
       <c r="R8" t="n">
-        <v>6949845</v>
+        <v>6949843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,15 +1421,131 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119816036</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489554</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6949859</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38156-2024 artfynd.xlsx
+++ b/artfynd/A 38156-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815905</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815902</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,8 +1586,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816036</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>